--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-reference-item-prescription.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4209,7 +4209,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>157</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>74</v>
@@ -4514,7 +4514,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>165</v>
       </c>
@@ -4529,13 +4529,13 @@
         <v>62</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>74</v>
@@ -4617,7 +4617,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>169</v>
       </c>
@@ -4632,13 +4632,13 @@
         <v>170</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>74</v>
@@ -4926,7 +4926,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>183</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
